--- a/output/pdf_financials_xlsx/KNT.xlsx
+++ b/output/pdf_financials_xlsx/KNT.xlsx
@@ -1260,19 +1260,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.31278</v>
+        <v>-0.31278</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.181119</v>
+        <v>-0.181119</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.13724</v>
+        <v>-0.13724</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.100022</v>
+        <v>-0.100022</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.317936</v>
+        <v>-0.317936</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.31278</v>
+        <v>-0.31278</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.181119</v>
+        <v>-0.181119</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.13724</v>
+        <v>-0.13724</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.100022</v>
+        <v>-0.100022</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.317936</v>
+        <v>-0.317936</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.31278</v>
+        <v>-0.31278</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.181119</v>
+        <v>-0.181119</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.13724</v>
+        <v>-0.13724</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.100022</v>
+        <v>-0.100022</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.317936</v>
+        <v>-0.317936</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>10.426</v>
+        <v>-10.426</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>15.8968</v>
+        <v>-15.8968</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.31278</v>
+        <v>-0.31278</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.181119</v>
+        <v>-0.181119</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.13724</v>
+        <v>-0.13724</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.100022</v>
+        <v>-0.100022</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.317936</v>
+        <v>-0.317936</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2099,19 +2099,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.31278</v>
+        <v>-0.31278</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.181119</v>
+        <v>-0.181119</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.13724</v>
+        <v>-0.13724</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.100022</v>
+        <v>-0.100022</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.317936</v>
+        <v>-0.317936</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2229,19 +2229,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -5763,19 +5763,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.146081</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.168936</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.168936</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.146081</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.146081</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0.146081</v>
@@ -20722,7 +20722,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -21590,7 +21594,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -21974,7 +21982,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -23138,7 +23150,11 @@
           <t>Reserves (Note 5b) 168,936</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>0.146081</v>
       </c>
@@ -61021,19 +61037,19 @@
         </is>
       </c>
       <c r="F556" s="5" t="n">
-        <v>0.31278</v>
+        <v>-0.31278</v>
       </c>
       <c r="G556" s="5" t="n">
-        <v>0.181119</v>
+        <v>-0.181119</v>
       </c>
       <c r="H556" s="5" t="n">
-        <v>0.13724</v>
+        <v>-0.13724</v>
       </c>
       <c r="I556" s="5" t="n">
-        <v>0.100022</v>
+        <v>-0.100022</v>
       </c>
       <c r="J556" s="5" t="n">
-        <v>0.317936</v>
+        <v>-0.317936</v>
       </c>
       <c r="K556" t="inlineStr">
         <is>
@@ -61777,10 +61793,10 @@
         </is>
       </c>
       <c r="H564" s="5" t="n">
-        <v>0.13724</v>
+        <v>-0.13724</v>
       </c>
       <c r="I564" s="5" t="n">
-        <v>0.100022</v>
+        <v>-0.100022</v>
       </c>
       <c r="J564" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KNT.xlsx
+++ b/output/pdf_financials_xlsx/KNT.xlsx
@@ -923,10 +923,10 @@
         <v>0.061067</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.051176</v>
+        <v>0.100022</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.04575</v>
+        <v>0.320468</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>9.720663999999999</v>
@@ -980,10 +980,10 @@
         <v>-0.061067</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.051176</v>
+        <v>-0.100022</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.04575</v>
+        <v>-0.320468</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002532</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>2.921</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>2.496</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>5.181</v>
       </c>
     </row>
     <row r="13">
@@ -1995,7 +1995,7 @@
         <v>-0.100022</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.317936</v>
+        <v>-0.315404</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2015,19 +2015,19 @@
         <v>17.738</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>46.595</v>
+        <v>46.429</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>59.771</v>
+        <v>58.551</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>51.287</v>
+        <v>48.366</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>164.774</v>
+        <v>162.278</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>388.071</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="28">
@@ -2111,7 +2111,7 @@
         <v>-0.100022</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.317936</v>
+        <v>-0.315404</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
         <v>17.738</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>46.595</v>
+        <v>46.429</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>59.771</v>
+        <v>58.551</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>51.287</v>
+        <v>48.366</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>164.774</v>
+        <v>162.278</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>388.071</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="30">
@@ -2202,19 +2202,19 @@
         <v>11.14721131186174</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>30.19257934502287</v>
+        <v>30.08501483871804</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>31.76166133506212</v>
+        <v>31.11336656286865</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>25.61084617113181</v>
+        <v>24.15220593742978</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>46.99463526351666</v>
+        <v>46.28275954515249</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>65.19473363247985</v>
+        <v>64.32434157806229</v>
       </c>
     </row>
     <row r="31">
@@ -2361,22 +2361,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.214121</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.33554</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.104048</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.032297</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.021651</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.003035</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>7.669314</v>
@@ -2471,22 +2471,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.214121</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.33554</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.104048</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.032297</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.021651</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.003035</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>7.669314</v>
@@ -3131,22 +3131,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.215083</v>
+        <v>0.000962</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.349392</v>
+        <v>0.013852</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.117045</v>
+        <v>0.012997</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.040969</v>
+        <v>0.008671999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.021651</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.004127</v>
+        <v>0.001092</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.960396</v>
@@ -7602,31 +7602,31 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.235487</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.331204</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.418084</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.776</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-2.036</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-4.865</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-5.253</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-4.465</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-1.919</v>
       </c>
     </row>
     <row r="125">
@@ -7659,31 +7659,31 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.235487</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.331204</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.418084</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.776</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-2.036</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-4.865</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-5.253</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-4.465</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-1.919</v>
       </c>
     </row>
     <row r="126">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
@@ -25730,7 +25730,11 @@
           <t>Principal lease payments (Note 10)</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -29726,7 +29730,11 @@
           <t>Principal lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -33662,7 +33670,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -34522,7 +34534,11 @@
           <t>Principal lease payments</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -50320,7 +50336,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -56890,7 +56906,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -60830,7 +60846,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -60928,7 +60944,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">

--- a/output/pdf_financials_xlsx/KNT.xlsx
+++ b/output/pdf_financials_xlsx/KNT.xlsx
@@ -1002,22 +1002,22 @@
         <v>39.9945</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>85.70099999999999</v>
+        <v>69.167</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>71.029</v>
+        <v>47.518</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>91.914</v>
+        <v>63.355</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88.867</v>
+        <v>52.269</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>208.386</v>
+        <v>163.231</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>438.337</v>
+        <v>384.008</v>
       </c>
     </row>
     <row r="12">
@@ -1283,10 +1283,10 @@
         <v>-12.069037</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>39.056954</v>
+        <v>12.586521</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>32.542453</v>
+        <v>29.358198</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>17.738</v>
@@ -1340,10 +1340,10 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>26.470433</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>3.184255</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>24.296</v>
@@ -2006,10 +2006,10 @@
         <v>-12.069037</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>39.056954</v>
+        <v>12.586521</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>32.542453</v>
+        <v>29.358198</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>17.738</v>
@@ -2122,10 +2122,10 @@
         <v>-12.069037</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>39.056954</v>
+        <v>12.586521</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>32.542453</v>
+        <v>29.358198</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>17.738</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>73.4695260341868</v>
+        <v>23.67634025657349</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>32.00080733504699</v>
+        <v>28.86955196346637</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>11.14721131186174</v>
@@ -2252,10 +2252,10 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>210.3077808395187</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>10.84622087500057</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>136.9714736723419</v>
@@ -6789,16 +6789,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.145118</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.059624</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.150659</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.164867</v>
       </c>
       <c r="L110" s="3" t="n">
         <v>0</v>
@@ -33008,7 +33008,11 @@
           <t>Accretion expense (Note 12)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -38748,7 +38752,11 @@
           <t>Accretion expense (Note 13) -</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -43178,7 +43186,11 @@
           <t>Accretion expense (Note 13) 59,624</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -49534,7 +49546,11 @@
           <t>Earnings from mine operations $</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -50154,7 +50170,11 @@
           <t>Earnings from operations $</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -51632,7 +51652,11 @@
           <t>Earnings from mine operations</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -54434,7 +54458,11 @@
           <t>Deferred income tax recovery (Note 21)</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
